--- a/Output/Supplement/EdgeWeightsExcel_half.xlsx
+++ b/Output/Supplement/EdgeWeightsExcel_half.xlsx
@@ -1097,7 +1097,7 @@
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>0.195084855528764</v>
+        <v>0.195084855528765</v>
       </c>
       <c r="G2" t="n">
         <v>0.283864405155383</v>
@@ -1105,23 +1105,23 @@
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.039285243870159</v>
+        <v>0.0392852438701586</v>
       </c>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2" t="n">
-        <v>0.29665924724257</v>
+        <v>0.296659247242571</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0834508597522578</v>
+        <v>-0.0834508597522583</v>
       </c>
       <c r="O2"/>
       <c r="P2" t="n">
-        <v>0.0632143069363741</v>
+        <v>0.0632143069363746</v>
       </c>
       <c r="Q2"/>
       <c r="R2" t="n">
-        <v>0.0730299192922901</v>
+        <v>0.07302991929229</v>
       </c>
       <c r="S2"/>
       <c r="T2"/>
@@ -1129,7 +1129,7 @@
         <v>0.343791955427362</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0864135740044472</v>
+        <v>0.086413574004448</v>
       </c>
       <c r="W2"/>
       <c r="X2"/>
@@ -1150,7 +1150,7 @@
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3" t="n">
-        <v>0.177928667397783</v>
+        <v>0.177928667397784</v>
       </c>
       <c r="N3"/>
       <c r="O3"/>
@@ -1160,11 +1160,11 @@
       <c r="S3"/>
       <c r="T3"/>
       <c r="U3" t="n">
-        <v>0.954076794686476</v>
+        <v>0.954076794686477</v>
       </c>
       <c r="V3"/>
       <c r="W3" t="n">
-        <v>0.061566320751954</v>
+        <v>0.0615663207519542</v>
       </c>
       <c r="X3"/>
     </row>
@@ -1176,7 +1176,7 @@
       <c r="C4"/>
       <c r="D4"/>
       <c r="E4" t="n">
-        <v>0.165442650835118</v>
+        <v>0.165442650835117</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
@@ -1184,14 +1184,14 @@
         <v>-0.0342602010432672</v>
       </c>
       <c r="I4" t="n">
-        <v>0.196262184691042</v>
+        <v>0.196262184691043</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
       <c r="N4" t="n">
-        <v>0.232884899991254</v>
+        <v>0.232884899991253</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
@@ -1199,12 +1199,12 @@
       <c r="R4"/>
       <c r="S4"/>
       <c r="T4" t="n">
-        <v>-0.0781616243603974</v>
+        <v>-0.0781616243603976</v>
       </c>
       <c r="U4"/>
       <c r="V4"/>
       <c r="W4" t="n">
-        <v>-0.0389158360761881</v>
+        <v>-0.0389158360761883</v>
       </c>
       <c r="X4"/>
     </row>
@@ -1233,7 +1233,7 @@
       <c r="T5"/>
       <c r="U5"/>
       <c r="V5" t="n">
-        <v>0.112728579150755</v>
+        <v>0.112728579150754</v>
       </c>
       <c r="W5"/>
       <c r="X5"/>
@@ -1251,7 +1251,7 @@
         <v>0.147442009291539</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0597056293702249</v>
+        <v>-0.0597056293702252</v>
       </c>
       <c r="I6" t="n">
         <v>0.139961790320562</v>
@@ -1261,16 +1261,16 @@
       </c>
       <c r="K6"/>
       <c r="L6" t="n">
-        <v>0.087058600087681</v>
+        <v>0.087058600087677</v>
       </c>
       <c r="M6" t="n">
-        <v>0.085565170216615</v>
+        <v>0.0855651702166149</v>
       </c>
       <c r="N6" t="n">
         <v>-0.258714170229548</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0859495875959826</v>
+        <v>-0.0859495875959825</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
@@ -1279,16 +1279,16 @@
       </c>
       <c r="S6"/>
       <c r="T6" t="n">
-        <v>0.0847372190075982</v>
+        <v>0.0847372190075981</v>
       </c>
       <c r="U6" t="n">
         <v>0.119100351553242</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0367049375696989</v>
+        <v>-0.036704937569699</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0388629662038811</v>
+        <v>0.0388629662038822</v>
       </c>
       <c r="X6" t="n">
         <v>0.16818455811866</v>
@@ -1305,10 +1305,10 @@
       <c r="F7"/>
       <c r="G7"/>
       <c r="H7" t="n">
-        <v>0.0492865754816253</v>
+        <v>0.0492865754816255</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0306509422514931</v>
+        <v>0.030650942251493</v>
       </c>
       <c r="J7"/>
       <c r="K7" t="n">
@@ -1323,29 +1323,29 @@
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
-        <v>0.0807476140269174</v>
+        <v>0.0807476140269171</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0590320460193886</v>
+        <v>-0.0590320460193885</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0294270276917267</v>
+        <v>0.0294270276917272</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0363978281694252</v>
+        <v>0.0363978281694253</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0400835890317947</v>
+        <v>0.0400835890317946</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0721007956383387</v>
+        <v>0.0721007956383382</v>
       </c>
       <c r="V7"/>
       <c r="W7" t="n">
-        <v>-0.0524321209983798</v>
+        <v>-0.0524321209983801</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0817531575855364</v>
+        <v>-0.0817531575855365</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1362,7 @@
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8" t="n">
-        <v>0.0468830077040953</v>
+        <v>0.046883007704095</v>
       </c>
       <c r="L8"/>
       <c r="M8"/>
@@ -1371,19 +1371,19 @@
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8" t="n">
-        <v>0.0448181276859438</v>
+        <v>0.0448181276859439</v>
       </c>
       <c r="S8"/>
       <c r="T8"/>
       <c r="U8"/>
       <c r="V8" t="n">
-        <v>-0.19618131296184</v>
+        <v>-0.196181312961841</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0553239051482226</v>
+        <v>-0.0553239051482229</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0549132544269569</v>
+        <v>-0.0549132544269567</v>
       </c>
     </row>
     <row r="9">
@@ -1399,34 +1399,34 @@
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="n">
-        <v>0.0984666467086239</v>
+        <v>0.0984666467086265</v>
       </c>
       <c r="K9"/>
       <c r="L9" t="n">
-        <v>0.0630136749941603</v>
+        <v>0.0630136749941572</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0416223429306809</v>
+        <v>0.0416223429306814</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0291047514495705</v>
+        <v>0.0291047514495704</v>
       </c>
       <c r="O9"/>
       <c r="P9" t="n">
-        <v>-0.0186114817250301</v>
+        <v>-0.0186114817250302</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0426862487855902</v>
+        <v>0.0426862487855903</v>
       </c>
       <c r="R9"/>
       <c r="S9"/>
       <c r="T9"/>
       <c r="U9"/>
       <c r="V9" t="n">
-        <v>0.0993525900439889</v>
+        <v>0.0993525900439892</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0331350252051727</v>
+        <v>0.033135025205173</v>
       </c>
       <c r="X9"/>
     </row>
@@ -1445,7 +1445,7 @@
       <c r="J10"/>
       <c r="K10"/>
       <c r="L10" t="n">
-        <v>0.708188155667581</v>
+        <v>0.708188155667568</v>
       </c>
       <c r="M10"/>
       <c r="N10"/>
@@ -1458,7 +1458,7 @@
       <c r="U10"/>
       <c r="V10"/>
       <c r="W10" t="n">
-        <v>-0.0840801633464388</v>
+        <v>-0.0840801633464393</v>
       </c>
       <c r="X10"/>
     </row>
@@ -1479,25 +1479,25 @@
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11" t="n">
-        <v>-0.0783544291003575</v>
+        <v>-0.0783544291003571</v>
       </c>
       <c r="O11"/>
       <c r="P11"/>
       <c r="Q11" t="n">
-        <v>0.0659169355189085</v>
+        <v>0.0659169355189081</v>
       </c>
       <c r="R11" t="n">
-        <v>0.11872145004869</v>
+        <v>0.118721450048689</v>
       </c>
       <c r="S11"/>
       <c r="T11"/>
       <c r="U11"/>
       <c r="V11"/>
       <c r="W11" t="n">
-        <v>0.11215855832279</v>
+        <v>0.112158558322789</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.195611240610624</v>
+        <v>-0.195611240610622</v>
       </c>
     </row>
     <row r="12">
@@ -1516,14 +1516,14 @@
       <c r="K12"/>
       <c r="L12"/>
       <c r="M12" t="n">
-        <v>0.0422431341027043</v>
+        <v>0.042243134102705</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.076851574084693</v>
+        <v>-0.0768515740846925</v>
       </c>
       <c r="O12"/>
       <c r="P12" t="n">
-        <v>-0.0323858095864363</v>
+        <v>-0.0323858095864358</v>
       </c>
       <c r="Q12"/>
       <c r="R12"/>
@@ -1554,7 +1554,7 @@
       <c r="O13"/>
       <c r="P13"/>
       <c r="Q13" t="n">
-        <v>-0.0448132214556738</v>
+        <v>-0.0448132214556739</v>
       </c>
       <c r="R13"/>
       <c r="S13"/>
@@ -1564,10 +1564,10 @@
       </c>
       <c r="V13"/>
       <c r="W13" t="n">
-        <v>0.120845888474301</v>
+        <v>0.120845888474302</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0616515767935341</v>
+        <v>0.0616515767935342</v>
       </c>
     </row>
     <row r="14">
@@ -1598,20 +1598,20 @@
       </c>
       <c r="R14"/>
       <c r="S14" t="n">
-        <v>-0.0529732654576609</v>
+        <v>-0.052973265457661</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0416290174555944</v>
+        <v>-0.0416290174555947</v>
       </c>
       <c r="U14"/>
       <c r="V14" t="n">
         <v>-0.0525548782888436</v>
       </c>
       <c r="W14" t="n">
-        <v>0.136649773846829</v>
+        <v>0.13664977384683</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0547294085541452</v>
+        <v>0.0547294085541449</v>
       </c>
     </row>
     <row r="15">
@@ -1639,7 +1639,7 @@
         <v>0.129280283278855</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.0588912167177525</v>
+        <v>-0.0588912167177524</v>
       </c>
       <c r="S15"/>
       <c r="T15"/>
@@ -1672,15 +1672,15 @@
       </c>
       <c r="R16"/>
       <c r="S16" t="n">
-        <v>0.0496727094453582</v>
+        <v>0.0496727094453581</v>
       </c>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16" t="n">
-        <v>-0.270638363729084</v>
+        <v>-0.270638363729085</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0566323206157543</v>
+        <v>0.0566323206157545</v>
       </c>
       <c r="X16"/>
     </row>
@@ -1742,13 +1742,13 @@
       <c r="Q18"/>
       <c r="R18"/>
       <c r="S18" t="n">
-        <v>0.0897017985502244</v>
+        <v>0.0897017985502245</v>
       </c>
       <c r="T18" t="n">
-        <v>0.174797727071569</v>
+        <v>0.17479772707157</v>
       </c>
       <c r="U18" t="n">
-        <v>0.067087113978241</v>
+        <v>0.0670871139782408</v>
       </c>
       <c r="V18"/>
       <c r="W18"/>
@@ -1777,14 +1777,14 @@
       <c r="R19"/>
       <c r="S19"/>
       <c r="T19" t="n">
-        <v>0.0250991888540529</v>
+        <v>0.0250991888540531</v>
       </c>
       <c r="U19"/>
       <c r="V19" t="n">
         <v>0.0401252284369804</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0206516373544459</v>
+        <v>0.0206516373544461</v>
       </c>
       <c r="X19" t="n">
         <v>0.0299059705324472</v>
@@ -1815,13 +1815,13 @@
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20" t="n">
-        <v>-0.0338714767429168</v>
+        <v>-0.033871476742917</v>
       </c>
       <c r="W20" t="n">
-        <v>0.10608274416271</v>
+        <v>0.106082744162711</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0529307422609259</v>
+        <v>0.0529307422609256</v>
       </c>
     </row>
     <row r="21">
@@ -1880,7 +1880,7 @@
       <c r="U22"/>
       <c r="V22"/>
       <c r="W22" t="n">
-        <v>0.0442550904666215</v>
+        <v>0.0442550904666221</v>
       </c>
       <c r="X22"/>
     </row>
@@ -1911,7 +1911,7 @@
       <c r="V23"/>
       <c r="W23"/>
       <c r="X23" t="n">
-        <v>0.5027778768252</v>
+        <v>0.502777876825202</v>
       </c>
     </row>
     <row r="24">
